--- a/output/EMEAA/EMEAA_Intercompany/Output/EMEAA_Intercompany billing lines_April 2026.xlsx
+++ b/output/EMEAA/EMEAA_Intercompany/Output/EMEAA_Intercompany billing lines_April 2026.xlsx
@@ -1949,7 +1949,7 @@
       <c r="E10" s="177" t="n"/>
       <c r="F10" s="178" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G10" s="179" t="n"/>
